--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487822_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487822_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1168</v>
+        <v>4.6232</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1389</v>
+        <v>6.6746</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0221</v>
+        <v>-2.0515</v>
       </c>
       <c r="G2" t="n">
         <v>2.2916</v>
@@ -610,13 +610,13 @@
         <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.383</v>
+        <v>0.1235</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9134</v>
+        <v>-0.3776</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5305</v>
+        <v>0.5011</v>
       </c>
       <c r="V2" t="n">
         <v>1.1675</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8816</v>
+        <v>3.0769</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7465</v>
+        <v>1.8536</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1352</v>
+        <v>1.2232</v>
       </c>
       <c r="G3" t="n">
         <v>1.8229</v>
@@ -688,13 +688,13 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>0.475</v>
+        <v>0.6702</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1924</v>
+        <v>0.2996</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2825</v>
+        <v>0.3706</v>
       </c>
       <c r="V3" t="n">
         <v>0.5838</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1076</v>
+        <v>2.6243</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5478</v>
+        <v>1.9764</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5598</v>
+        <v>0.6479</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0621</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7085</v>
+        <v>-0.1918</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5219</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1866</v>
+        <v>-0.0985</v>
       </c>
       <c r="V4" t="n">
         <v>3.5026</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1859</v>
+        <v>1.0932</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4884</v>
+        <v>0.2691</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6975</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5936</v>
+        <v>2.4351</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9765</v>
+        <v>-2.7099</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3829</v>
+        <v>5.1451</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2061</v>
+        <v>4.0764</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1277</v>
+        <v>-2.028</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0784</v>
+        <v>6.1044</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-1.6412</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1512</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4613</v>
+        <v>-0.9593</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-4.5786</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4684</v>
+        <v>0.2804</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3229</v>
+        <v>-0.3962</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1455</v>
+        <v>0.6766</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1238</v>
+        <v>1.2914</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
         <v>0.1238</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1183</v>
+        <v>0.9613</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5295</v>
+        <v>0.3812</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5888</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8162</v>
+        <v>0.5936</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1688</v>
+        <v>0.9765</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6474</v>
+        <v>-0.3829</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6045</v>
+        <v>1.2061</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9978</v>
+        <v>1.1277</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6067</v>
+        <v>0.0784</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7883</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.829</v>
+        <v>-0.1512</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9593</v>
+        <v>-0.4613</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.4568</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6153</v>
+        <v>0.2438</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8482</v>
+        <v>0.2158</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4634</v>
+        <v>0.0281</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9376</v>
+        <v>0.1238</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1675</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.8526</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0524</v>
+        <v>0.8509</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0296</v>
+        <v>0.0016</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4351</v>
+        <v>0.8162</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7099</v>
+        <v>0.1688</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1451</v>
+        <v>0.6474</v>
       </c>
       <c r="J7" t="n">
-        <v>4.0764</v>
+        <v>2.6045</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.028</v>
+        <v>0.9978</v>
       </c>
       <c r="L7" t="n">
-        <v>6.1044</v>
+        <v>1.6067</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6412</v>
+        <v>-1.7883</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.829</v>
       </c>
       <c r="O7" t="n">
         <v>-0.9593</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.9137</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5786</v>
+        <v>-1.4568</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1644</v>
+        <v>0.3495</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7177</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8821</v>
+        <v>0.8762</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2914</v>
+        <v>-0.9376</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1238</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1018</v>
+        <v>-0.14</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0897</v>
+        <v>0.8754</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1915</v>
+        <v>-1.0154</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1729</v>
@@ -1078,13 +1078,13 @@
         <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1964</v>
+        <v>-0.2345</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2829</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1278</v>
+        <v>0.0483</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3975</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-0.7635</v>
       </c>
       <c r="E9" t="n">
         <v>-0.8449</v>
       </c>
       <c r="F9" t="n">
-        <v>0.052</v>
+        <v>0.0814</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8124</v>
@@ -1156,13 +1156,13 @@
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3967</v>
+        <v>-0.3673</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2662</v>
+        <v>-0.2368</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8353</v>
+        <v>-1.4448</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2119</v>
+        <v>-1.9976</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3766</v>
+        <v>0.5528</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7474</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4417</v>
+        <v>-0.0512</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4567</v>
+        <v>-0.2424</v>
       </c>
       <c r="U10" t="n">
-        <v>0.015</v>
+        <v>0.1912</v>
       </c>
       <c r="V10" t="n">
         <v>-0.23</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8973</v>
+        <v>-3.123</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1314</v>
+        <v>-1.476</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0287</v>
+        <v>-1.647</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1241</v>
@@ -1312,13 +1312,13 @@
         <v>2.7055</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7699</v>
+        <v>0.5442</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9441</v>
+        <v>0.3367</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1742</v>
+        <v>0.2075</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7513</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.760300000000001</v>
+        <v>7.760199999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>8.562999999999999</v>
+        <v>8.5627</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8028000000000002</v>
+        <v>-0.8028</v>
       </c>
       <c r="G12" t="n">
         <v>4.0405</v>
@@ -1378,10 +1378,10 @@
         <v>-4.6558</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.103000000000001</v>
+        <v>-7.103</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.999999999971143e-05</v>
+        <v>-9.999999999982245e-05</v>
       </c>
       <c r="Q12" t="n">
         <v>-15.6088</v>
@@ -1390,13 +1390,13 @@
         <v>15.6088</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3667</v>
+        <v>1.3668</v>
       </c>
       <c r="T12" t="n">
         <v>-1.1975</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5642</v>
+        <v>2.564299999999999</v>
       </c>
       <c r="V12" t="n">
         <v>2.352700000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2809</v>
+        <v>3.6878</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9461</v>
+        <v>4.0888</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6652</v>
+        <v>-0.401</v>
       </c>
       <c r="G13" t="n">
         <v>2.8839</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9401</v>
+        <v>0.3471</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.0496</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0333</v>
+        <v>0.2975</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5838</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.971</v>
+        <v>1.8051</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6924</v>
+        <v>3.5852</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7214</v>
+        <v>-1.7801</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0688</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0515</v>
+        <v>-0.2174</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1338</v>
+        <v>-0.2409</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0823</v>
+        <v>0.0235</v>
       </c>
       <c r="V14" t="n">
         <v>1.0508</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.433</v>
+        <v>-0.3068</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0269</v>
+        <v>0.1874</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4062</v>
+        <v>-0.4942</v>
       </c>
       <c r="G15" t="n">
         <v>0.3241</v>
@@ -1624,13 +1624,13 @@
         <v>0.2081</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2023</v>
+        <v>0.3285</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1491</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2675</v>
+        <v>0.1794</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1675</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6852</v>
+        <v>-0.4811</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2946</v>
+        <v>0.0269</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3906</v>
+        <v>-0.5081</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0859</v>
@@ -1702,13 +1702,13 @@
         <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5598</v>
+        <v>-0.3557</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1744</v>
+        <v>-0.8529</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6146</v>
+        <v>0.4972</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2477</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.479</v>
+        <v>-1.0607</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9251</v>
+        <v>-2.3894</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4461</v>
+        <v>1.3287</v>
       </c>
       <c r="G17" t="n">
         <v>0.7946</v>
@@ -1780,13 +1780,13 @@
         <v>2.9137</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3484</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7177</v>
+        <v>-0.1819</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3693</v>
+        <v>0.2519</v>
       </c>
       <c r="V17" t="n">
         <v>1.4046</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0261</v>
+        <v>-1.48</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2421</v>
+        <v>0.6707</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2682</v>
+        <v>-2.1507</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3844</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2357</v>
+        <v>-0.6896</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7829</v>
+        <v>-0.3543</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4527</v>
+        <v>-0.3353</v>
       </c>
       <c r="V18" t="n">
         <v>1.6345</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3316</v>
+        <v>-2.292</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8686</v>
+        <v>0.7614</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2002</v>
+        <v>-3.0534</v>
       </c>
       <c r="G19" t="n">
         <v>-1.223</v>
@@ -1936,13 +1936,13 @@
         <v>2.0812</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2812</v>
+        <v>-0.2416</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1338</v>
+        <v>-0.2409</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1474</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-1.868</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3774</v>
+        <v>-2.3202</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3421</v>
+        <v>-4.0206</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9647</v>
+        <v>1.7004</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4195</v>
@@ -2014,13 +2014,13 @@
         <v>2.0812</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.291</v>
+        <v>-0.2337</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8482</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5572</v>
+        <v>0.293</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7076</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6797</v>
+        <v>-5.3123</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3576</v>
+        <v>-2.1077</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.322</v>
+        <v>-3.2046</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8618</v>
@@ -2092,13 +2092,13 @@
         <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2583</v>
+        <v>-0.3743</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3849</v>
+        <v>-0.3652</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1265</v>
+        <v>-0.0091</v>
       </c>
       <c r="V21" t="n">
         <v>-1.868</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.7601</v>
+        <v>-7.760199999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.8026999999999993</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.563000000000001</v>
+        <v>-8.562999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-4.040800000000001</v>
@@ -2170,13 +2170,13 @@
         <v>15.609</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3669</v>
+        <v>-1.3667</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.5643</v>
+        <v>-2.5641</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1976</v>
+        <v>1.1975</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3527</v>
